--- a/AAII_Financials/Quarterly/FNBKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FNBKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="92">
   <si>
     <t>FNBKY</t>
   </si>
@@ -656,79 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -768,8 +772,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -809,8 +816,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +860,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -867,8 +880,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -908,8 +922,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -949,8 +966,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -990,8 +1010,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,8 +1054,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,8 +1071,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1086,8 +1113,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1127,8 +1157,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1144,8 +1177,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1185,8 +1219,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1226,8 +1263,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1267,8 +1307,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1308,8 +1351,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1349,8 +1395,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1390,8 +1439,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1431,8 +1483,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1472,8 +1527,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1513,8 +1571,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1554,8 +1615,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1595,8 +1659,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1636,8 +1703,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1677,8 +1747,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1718,8 +1791,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1759,8 +1835,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1800,54 +1879,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1863,8 +1948,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1880,131 +1966,141 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2090100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2201000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1883700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2032200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3036500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2505300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1657900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1570700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1612300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1902900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1657900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>1570700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>815900</v>
+      </c>
+      <c r="E42" s="3">
         <v>834700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>831300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>805600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1099500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1020600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1419700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1760600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1239400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1111100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1419700</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>1760600</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>463700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1018200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1010600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1319000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1408500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1806100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1475000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1184700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>879700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1541700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1475000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>1184700</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2044,213 +2140,231 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>593800</v>
+      </c>
+      <c r="E45" s="3">
         <v>832300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>413400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>518200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>336100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>394400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>363600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>414800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>382000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>363600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4339100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5249700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4489900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4968300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6183400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6023900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5239500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5263600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4435700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4555700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5239500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>5263600</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2786900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2974900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3043800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2527700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2338500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2934600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3315600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3886500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4342500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>22890300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3315600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>3886500</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>174500</v>
+      </c>
+      <c r="E48" s="3">
         <v>178500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>169300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>151500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>153000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>161900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>157000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>156300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>151600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>149400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>157000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>141300</v>
+      </c>
+      <c r="E49" s="3">
         <v>145100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>145800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>129300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>131900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>137100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>136900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>135100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>132900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>131700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>136900</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2290,8 +2404,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2331,49 +2448,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E52" s="3">
         <v>53000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>73600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>39400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>39100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>366400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2413,49 +2536,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44218900</v>
+      </c>
+      <c r="E54" s="3">
         <v>43790000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>41525800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35913500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35124600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36825100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36916900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38761200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37714500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35019900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36916900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>38761200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2471,8 +2600,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2488,254 +2618,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36934500</v>
+      </c>
+      <c r="E57" s="3">
         <v>37155800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35350700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30681500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30822000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31392600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31114100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32645600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33021900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31327300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31114100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>32645600</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1165800</v>
+      </c>
+      <c r="E58" s="3">
         <v>967700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>864000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>356600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>383500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>241200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>545200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1055000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>111400</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3">
         <v>545200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>1055000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1048300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1114800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>351700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1045000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>224800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1367500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1709200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2064100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1684100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>145300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1709200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>2064100</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39280900</v>
+      </c>
+      <c r="E60" s="3">
         <v>39395000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36689100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32232500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31485100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33134600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33480700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35879700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34899700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31463300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33480700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>35879700</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1558800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1011600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1698700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>899100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>925900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>962400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>946000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>599800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>588500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>854600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>946000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>599800</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>616100</v>
+      </c>
+      <c r="E62" s="3">
         <v>359100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>477400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>285500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>317100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>276200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>378100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>214900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>416600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>525900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>378100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>214900</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2775,8 +2924,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2816,8 +2968,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2857,49 +3012,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41480700</v>
+      </c>
+      <c r="E66" s="3">
         <v>40792000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38890100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33439800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32751600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34399300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34830200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36719600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35927700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32843800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34830200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>36719600</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2915,8 +3076,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2956,8 +3118,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2997,8 +3162,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3038,8 +3206,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3079,49 +3250,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1892200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2128800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1768500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1712800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1434500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1606500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1271800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1245400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1013000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>480700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1271800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>1245400</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3161,8 +3338,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3202,8 +3382,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3243,49 +3426,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2738100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2997900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2635700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2473700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2372900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2425900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2086700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2041700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1786800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2176100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2086700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2075600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2041700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3325,54 +3514,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3412,8 +3607,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3429,8 +3627,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3470,8 +3669,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3511,8 +3713,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3552,8 +3757,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3593,8 +3801,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3634,8 +3845,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3675,8 +3889,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3716,8 +3933,11 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3733,8 +3953,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3774,8 +3995,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3815,8 +4039,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3856,8 +4083,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3897,8 +4127,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3914,8 +4147,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3955,8 +4189,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3996,8 +4233,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4037,8 +4277,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4078,8 +4321,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4119,8 +4365,11 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4160,8 +4409,11 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4199,6 +4451,9 @@
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
